--- a/data/activités.xlsx
+++ b/data/activités.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Méthode &amp; lacunes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sorties'!$A$1:$V$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Services (hors sorties)'!$A$1:$V$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Nouveaux lieux trouvés'!$A$1:$M$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sorties'!$A$1:$W$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Services (hors sorties)'!$A$1:$W$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Nouveaux lieux trouvés'!$A$1:$N$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V154"/>
+  <dimension ref="A1:W154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -601,6 +601,11 @@
           <t>Transports (TPG)</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tags secondaires</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -11551,7 +11556,7 @@
       <c r="V154" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V154"/>
+  <autoFilter ref="A1:W154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11562,7 +11567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11699,6 +11704,11 @@
           <t>Transports (TPG)</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tags secondaires</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -14377,7 +14387,7 @@
       <c r="V41" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V41"/>
+  <autoFilter ref="A1:W41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14388,7 +14398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -14472,6 +14482,11 @@
           <t>Remarque</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tags secondaires</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -19293,7 +19308,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M86"/>
+  <autoFilter ref="A1:N86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
